--- a/public/uploads/user_template.xlsx
+++ b/public/uploads/user_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Form CR\public\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B88C69F-E218-4803-AB40-7F6BDA1C1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96B86E6-CB89-4A50-983C-DB34E80BD040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CAA851B6-73E0-4BD4-9438-C61F9A3ABD3C}"/>
   </bookViews>
@@ -36,31 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>NPK</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Role ID</t>
-  </si>
-  <si>
-    <t>Departement</t>
-  </si>
-  <si>
-    <t>User Status</t>
-  </si>
-  <si>
-    <t>Ext Phone</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Section Head</t>
   </si>
@@ -72,6 +48,33 @@
   </si>
   <si>
     <t>PPIC</t>
+  </si>
+  <si>
+    <t>npk</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>username</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>role_id</t>
+  </si>
+  <si>
+    <t>departement</t>
+  </si>
+  <si>
+    <t>user_status</t>
+  </si>
+  <si>
+    <t>ext_phone</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56AD6AE4-5E68-4844-9980-F0CF5D1FB9D7}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
@@ -467,56 +470,62 @@
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>12345</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>12345</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>22223</v>
+      </c>
+      <c r="I2">
+        <v>12345</v>
       </c>
     </row>
   </sheetData>

--- a/public/uploads/user_template.xlsx
+++ b/public/uploads/user_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Form CR\public\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96B86E6-CB89-4A50-983C-DB34E80BD040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A18069-EC5D-4062-AAEB-D8BCA09F73DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CAA851B6-73E0-4BD4-9438-C61F9A3ABD3C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Section Head</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>user</t>
   </si>
 </sst>
 </file>
@@ -512,8 +515,8 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" t="s">
+        <v>13</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>

--- a/public/uploads/user_template.xlsx
+++ b/public/uploads/user_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Form CR\public\uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Form CR - PO\public\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A18069-EC5D-4062-AAEB-D8BCA09F73DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CA0C56-BF71-49E5-8E65-8178AF38E6E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CAA851B6-73E0-4BD4-9438-C61F9A3ABD3C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Section Head</t>
   </si>
@@ -47,9 +47,6 @@
     <t>budiabcd@dac.dharmap.com</t>
   </si>
   <si>
-    <t>PPIC</t>
-  </si>
-  <si>
     <t>npk</t>
   </si>
   <si>
@@ -77,7 +74,13 @@
     <t>password</t>
   </si>
   <si>
-    <t>user</t>
+    <t>company_code</t>
+  </si>
+  <si>
+    <t>dh</t>
+  </si>
+  <si>
+    <t>PPIC, IT Development, Infra</t>
   </si>
 </sst>
 </file>
@@ -460,81 +463,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56AD6AE4-5E68-4844-9980-F0CF5D1FB9D7}">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>12345</v>
-      </c>
-      <c r="B2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B2">
+        <v>112155515</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>12345</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2">
+        <v>112155515</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>3</v>
-      </c>
       <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
         <v>0</v>
       </c>
-      <c r="H2">
-        <v>22223</v>
-      </c>
       <c r="I2">
-        <v>12345</v>
+        <v>12345678</v>
+      </c>
+      <c r="J2">
+        <v>112155515</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{9FBE32F7-8443-4B49-9518-351C40140AA4}">
+      <formula1>"user,dh,divh,it"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2" xr:uid="{3D58E7A1-8D70-407E-8D23-9F01ED2CC8FE}">
+      <formula1>"1100,1200,1300,1400,1500,1600,1700"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{800C0B3A-B7C0-47C8-85C7-F2E6706B1F0B}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{800C0B3A-B7C0-47C8-85C7-F2E6706B1F0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>